--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,21 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +630,9 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +719,9 @@
       <c r="T3" t="n">
         <v>19.39</v>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -787,6 +808,9 @@
       <c r="T4" t="n">
         <v>19</v>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -873,6 +897,9 @@
       <c r="T5" t="n">
         <v>16.97</v>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,6 +986,9 @@
       <c r="T6" t="n">
         <v>17.59</v>
       </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,6 +1075,9 @@
       <c r="T7" t="n">
         <v>11.59</v>
       </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1131,6 +1164,9 @@
       <c r="T8" t="n">
         <v>14.39</v>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1217,6 +1253,9 @@
       <c r="T9" t="n">
         <v>13.2</v>
       </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1303,6 +1342,9 @@
       <c r="T10" t="n">
         <v>17.59</v>
       </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1389,6 +1431,9 @@
       <c r="T11" t="n">
         <v>14.39</v>
       </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1475,6 +1520,9 @@
       <c r="T12" t="n">
         <v>15.32</v>
       </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1561,6 +1609,9 @@
       <c r="T13" t="n">
         <v>13.58</v>
       </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1647,6 +1698,9 @@
       <c r="T14" t="n">
         <v>5.14</v>
       </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,6 +1787,9 @@
       <c r="T15" t="n">
         <v>16.38</v>
       </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1819,6 +1876,9 @@
       <c r="T16" t="n">
         <v>-100</v>
       </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1905,6 +1965,9 @@
       <c r="T17" t="n">
         <v>14.39</v>
       </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1991,6 +2054,9 @@
       <c r="T18" t="n">
         <v>10.79</v>
       </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2077,6 +2143,9 @@
       <c r="T19" t="n">
         <v>16.38</v>
       </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2163,6 +2232,9 @@
       <c r="T20" t="n">
         <v>-100</v>
       </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2249,6 +2321,9 @@
       <c r="T21" t="n">
         <v>-100</v>
       </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2334,6 +2409,167 @@
       </c>
       <c r="T22" t="n">
         <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Junior x Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>12</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3x3</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>U. de Deportes x Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,37 +642,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UKRAINE 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fc Kharkiv x Obolon-Brovar Kiev</t>
+          <t>Fujieda Myfc x Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fc Kharkiv</t>
+          <t>Fujieda Myfc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Obolon-Brovar Kiev</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -681,45 +681,43 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>20.41</v>
+        <v>8.33</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.95</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8.039999999999999</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
@@ -731,27 +729,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>UKRAINE 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dalian Yingbo x Qingdao Hainiu</t>
+          <t>Fc Kharkiv x Obolon-Brovar Kiev</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Yingbo</t>
+          <t>Fc Kharkiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Obolon-Brovar Kiev</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -770,20 +768,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>20.41</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -806,7 +804,7 @@
         <v>0.95</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>19.39</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -820,37 +818,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Slavia Prague x FC Zbrojovka Brno</t>
+          <t>Fukuoka x Mito</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Prague</t>
+          <t>Fukuoka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>Mito</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -859,45 +857,43 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17.86</v>
+        <v>7.41</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.95</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7.15</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
@@ -909,37 +905,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bandirmaspor x Boluspor</t>
+          <t>Stoke x Charlton</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bandirmaspor</t>
+          <t>Stoke</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Charlton</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -948,45 +944,43 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18.52</v>
+        <v>7.41</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.95</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>17.59</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7.15</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
@@ -998,27 +992,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Man City x Coventry</t>
+          <t>Dalian Yingbo x Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,20 +1031,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="L7" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1073,7 +1067,7 @@
         <v>0.95</v>
       </c>
       <c r="T7" t="n">
-        <v>11.59</v>
+        <v>19</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1087,27 +1081,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORWAY 2</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Haugesund x Sogndal</t>
+          <t>Slavia Prague x FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Slavia Prague</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1126,20 +1120,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="L8" t="n">
-        <v>15.15</v>
+        <v>17.86</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1162,7 +1156,7 @@
         <v>0.95</v>
       </c>
       <c r="T8" t="n">
-        <v>14.39</v>
+        <v>16.97</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1176,27 +1170,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NORWAY 2</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kongsvinger x Raufoss</t>
+          <t>Bandirmaspor x Boluspor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bandirmaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1215,20 +1209,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="L9" t="n">
-        <v>13.89</v>
+        <v>18.52</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9x1</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1251,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="T9" t="n">
-        <v>13.2</v>
+        <v>17.59</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1270,22 +1264,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rosenborg x Ham-Kam</t>
+          <t>Man City x Coventry</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1304,20 +1298,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="L10" t="n">
-        <v>18.52</v>
+        <v>12.2</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1340,7 +1334,7 @@
         <v>0.95</v>
       </c>
       <c r="T10" t="n">
-        <v>17.59</v>
+        <v>11.59</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1354,37 +1348,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>NORWAY 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spartak Varna x CSKA Sofia</t>
+          <t>Haugesund x Sogndal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1396,7 +1390,7 @@
         <v>7.6</v>
       </c>
       <c r="K11" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="L11" t="n">
         <v>15.15</v>
@@ -1406,7 +1400,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1443,37 +1437,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>NORWAY 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SK Artis Brno x Plzen</t>
+          <t>Kongsvinger x Raufoss</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plzen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1482,20 +1476,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="L12" t="n">
-        <v>16.13</v>
+        <v>13.89</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>9x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1518,7 +1512,7 @@
         <v>0.95</v>
       </c>
       <c r="T12" t="n">
-        <v>15.32</v>
+        <v>13.2</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1532,27 +1526,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maritimo x Benfica</t>
+          <t>Rosenborg x Ham-Kam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1571,20 +1565,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="L13" t="n">
-        <v>14.29</v>
+        <v>18.52</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1607,7 +1601,7 @@
         <v>0.95</v>
       </c>
       <c r="T13" t="n">
-        <v>13.58</v>
+        <v>17.59</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1621,37 +1615,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARGENTINA 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata x Tigre</t>
+          <t>Spartak Varna x CSKA Sofia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1660,20 +1654,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19.5</v>
+        <v>7.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="L14" t="n">
-        <v>5.41</v>
+        <v>15.15</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1696,7 +1690,7 @@
         <v>0.95</v>
       </c>
       <c r="T14" t="n">
-        <v>5.14</v>
+        <v>14.39</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1710,37 +1704,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NORWAY 2</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stabaek x Moss</t>
+          <t>SK Artis Brno x Plzen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1749,20 +1743,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K15" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="L15" t="n">
-        <v>17.24</v>
+        <v>16.13</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1785,7 +1779,7 @@
         <v>0.95</v>
       </c>
       <c r="T15" t="n">
-        <v>16.38</v>
+        <v>15.32</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1799,37 +1793,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al-Ittihad x Al Nassr</t>
+          <t>Maritimo x Benfica</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1838,43 +1832,43 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="L16" t="n">
-        <v>21.28</v>
+        <v>14.29</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.7</v>
+        <v>0.95</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>-4.7</v>
+        <v>0.95</v>
       </c>
       <c r="T16" t="n">
-        <v>-100</v>
+        <v>13.58</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1888,37 +1882,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>St Mirren x Celtic</t>
+          <t>Gimnasia La Plata x Tigre</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Mirren</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1927,20 +1921,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="K17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="L17" t="n">
-        <v>15.15</v>
+        <v>5.41</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1963,7 +1957,7 @@
         <v>0.95</v>
       </c>
       <c r="T17" t="n">
-        <v>14.39</v>
+        <v>5.14</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1977,27 +1971,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>NORWAY 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sporting Lisbon x CD Nacional Funchal</t>
+          <t>Stabaek x Moss</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2016,20 +2010,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="L18" t="n">
-        <v>11.36</v>
+        <v>17.24</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2052,7 +2046,7 @@
         <v>0.95</v>
       </c>
       <c r="T18" t="n">
-        <v>10.79</v>
+        <v>16.38</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -2066,37 +2060,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cusco FC x Cesar Vallejo Moquegua</t>
+          <t>Al-Ittihad x Al Nassr</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cesar Vallejo Moquegua</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2105,43 +2099,43 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="K19" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="L19" t="n">
-        <v>17.24</v>
+        <v>21.28</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.95</v>
+        <v>-4.7</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.95</v>
+        <v>-4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>16.38</v>
+        <v>-100</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2155,37 +2149,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>SCOTLAND 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Inter Miami CF x Atlanta Utd</t>
+          <t>St Mirren x Celtic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>St Mirren</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2194,43 +2188,43 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K20" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="L20" t="n">
-        <v>15.62</v>
+        <v>15.15</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.4</v>
+        <v>0.95</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>-6.4</v>
+        <v>0.95</v>
       </c>
       <c r="T20" t="n">
-        <v>-100</v>
+        <v>14.39</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2244,27 +2238,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla x Jaguares de Cordoba</t>
+          <t>Sporting Lisbon x CD Nacional Funchal</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2283,43 +2277,43 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="L21" t="n">
-        <v>23.26</v>
+        <v>11.36</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3</v>
+        <v>0.95</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>-4.3</v>
+        <v>0.95</v>
       </c>
       <c r="T21" t="n">
-        <v>-100</v>
+        <v>10.79</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2333,7 +2327,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2343,17 +2337,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Universitario de Deportes x Comerciantes Unidos</t>
+          <t>Cusco FC x Cesar Vallejo Moquegua</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Cesar Vallejo Moquegua</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2372,43 +2366,43 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="K22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>17.24</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5</v>
+        <v>0.95</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>-5</v>
+        <v>0.95</v>
       </c>
       <c r="T22" t="n">
-        <v>-100</v>
+        <v>16.38</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2422,29 +2416,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Junior x Jaguares de Cordoba</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Inter Miami CF x Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2453,45 +2455,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="K23" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="L23" t="n">
-        <v>9.09</v>
+        <v>15.62</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2506,24 +2510,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>U. de Deportes x Comerciantes Unidos</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>Junior FC Barranquilla x Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2532,41 +2544,290 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="K24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="L24" t="n">
-        <v>7.41</v>
+        <v>23.26</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>3x3</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes x Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>2x2</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Junior x Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M26" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>3x3</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>U. de Deportes x Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
         <v>7.15</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>1</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,19 +694,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -870,19 +870,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -957,19 +957,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S6" t="n">
